--- a/139/merge/139/merge/StreamingAssets/Dialog.xlsx
+++ b/139/merge/139/merge/StreamingAssets/Dialog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="204">
   <si>
     <t>SpeakerName</t>
   </si>
@@ -507,7 +507,7 @@
 この先に、何が待っているんだろう）</t>
   </si>
   <si>
-    <t>（空間が変わる。私とセリカの前に、五枚の札が浮かび上がる）</t>
+    <t>（空間が変わる。私とセリカの前に、三枚の札が浮かび上がる）</t>
   </si>
   <si>
     <t>「これが……商品？」</t>
@@ -522,16 +522,10 @@
     <t>壊れた約束：交わされた約束は果たされず、信頼が静かに失われた。</t>
   </si>
   <si>
-    <t>赦せなかった手紙：届かなかった謝罪の手紙。封を切らなかった理由は不明。</t>
+    <t>信じた罰：何もかも信じていた自分が、一番の愚か者だったと気づかされた。</t>
   </si>
   <si>
-    <t>笑顔の仮面：貼りつけられた笑顔の裏で、誰にも本音を見せなかった人物の記憶。</t>
-  </si>
-  <si>
-    <t>赤い傘の記憶：雨の日に交わされた言葉。傘はもう存在しない。</t>
-  </si>
-  <si>
-    <t>怒りの種：些細な言葉が心に傷を残し、怒りへと育った記憶。</t>
+    <t>触れてしまった温度：壊したかったはずの存在が、気づけば温もりとして胸に残っていた。</t>
   </si>
   <si>
     <t>（それぞれの札が、機械のような声で説明されていく）</t>
@@ -35581,6 +35575,9 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -35595,10 +35592,18 @@
       <c r="S11" s="3"/>
     </row>
     <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
@@ -35615,7 +35620,12 @@
       <c r="B13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
@@ -35649,7 +35659,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>173</v>
@@ -35671,17 +35681,12 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
@@ -35692,18 +35697,10 @@
       <c r="S16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="C17" s="3"/>
       <c r="E17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
@@ -35715,7 +35712,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>176</v>
@@ -35731,6 +35728,9 @@
       <c r="S18" s="3"/>
     </row>
     <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B19" s="5" t="s">
         <v>177</v>
       </c>
@@ -35745,9 +35745,6 @@
       <c r="S19" s="3"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="B20" s="5" t="s">
         <v>178</v>
       </c>
@@ -35763,12 +35760,17 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>179</v>
+      <c r="B21" s="2" t="s">
+        <v>154</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
@@ -35780,9 +35782,14 @@
     </row>
     <row r="22">
       <c r="B22" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
@@ -35796,14 +35803,14 @@
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>154</v>
+      <c r="B23" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -35815,6 +35822,9 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B24" s="5" t="s">
         <v>181</v>
       </c>
@@ -35878,18 +35888,10 @@
       <c r="S26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B27" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="C27" s="3"/>
       <c r="E27" s="3"/>
       <c r="G27" s="3"/>
       <c r="I27" s="3"/>
@@ -35900,18 +35902,10 @@
       <c r="S27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B28" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="C28" s="3"/>
       <c r="E28" s="3"/>
       <c r="G28" s="3"/>
       <c r="I28" s="3"/>
@@ -35922,6 +35916,9 @@
       <c r="S28" s="3"/>
     </row>
     <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B29" s="5" t="s">
         <v>186</v>
       </c>
@@ -35936,9 +35933,6 @@
       <c r="S29" s="3"/>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="s">
-        <v>187</v>
-      </c>
       <c r="C30" s="3"/>
       <c r="E30" s="3"/>
       <c r="G30" s="3"/>
@@ -35950,12 +35944,6 @@
       <c r="S30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>188</v>
-      </c>
       <c r="C31" s="3"/>
       <c r="E31" s="3"/>
       <c r="G31" s="3"/>
@@ -46603,31 +46591,9 @@
       <c r="Q998" s="3"/>
       <c r="S998" s="3"/>
     </row>
-    <row r="999">
-      <c r="C999" s="3"/>
-      <c r="E999" s="3"/>
-      <c r="G999" s="3"/>
-      <c r="I999" s="3"/>
-      <c r="K999" s="3"/>
-      <c r="M999" s="3"/>
-      <c r="O999" s="3"/>
-      <c r="Q999" s="3"/>
-      <c r="S999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="C1000" s="3"/>
-      <c r="E1000" s="3"/>
-      <c r="G1000" s="3"/>
-      <c r="I1000" s="3"/>
-      <c r="K1000" s="3"/>
-      <c r="M1000" s="3"/>
-      <c r="O1000" s="3"/>
-      <c r="Q1000" s="3"/>
-      <c r="S1000" s="3"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C1000 E2:E1000 G2:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C998 E2:E998 G2:G998 I2:I998 K2:K998 M2:M998 O2:O998 Q2:Q998 S2:S998">
       <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2">
@@ -46680,7 +46646,7 @@
     </row>
     <row r="2">
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -46700,7 +46666,7 @@
     </row>
     <row r="3">
       <c r="B3" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="4"/>
@@ -46715,7 +46681,7 @@
     </row>
     <row r="4">
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="4"/>
@@ -57743,10 +57709,10 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
@@ -57772,13 +57738,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D3" s="2">
         <v>5.0</v>
@@ -57794,16 +57760,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E4" s="3"/>
       <c r="G4" s="3"/>
@@ -57816,13 +57782,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -57838,10 +57804,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -57860,10 +57826,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -57882,10 +57848,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
